--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N98_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N98_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>92.7401192876986</v>
+        <v>15.07026938425102</v>
       </c>
       <c r="D2" t="n">
-        <v>92.09926654074413</v>
+        <v>14.96613081287092</v>
       </c>
       <c r="E2" t="n">
-        <v>28.94809375873188</v>
+        <v>4.70406523579393</v>
       </c>
       <c r="F2" t="n">
-        <v>28.76093941449941</v>
+        <v>4.673652654856154</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.84393177023485</v>
+        <v>5.662138912663164</v>
       </c>
       <c r="D3" t="n">
-        <v>34.5773877117453</v>
+        <v>5.618825503158612</v>
       </c>
       <c r="E3" t="n">
-        <v>28.94809375873188</v>
+        <v>4.70406523579393</v>
       </c>
       <c r="F3" t="n">
-        <v>28.76093941449941</v>
+        <v>4.673652654856154</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
